--- a/Excelfile/ItemDetails.xlsx
+++ b/Excelfile/ItemDetails.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suraj\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\InfoEge Automation Project\Feb_26-Practice_ArtifactID\Excelfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D9893FF-08F5-4BC9-87C9-0587A405F082}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80B9FC9-596D-4106-82E2-41177CB9E9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
     <t>items</t>
   </si>
@@ -34,6 +34,12 @@
   </si>
   <si>
     <t>shirts</t>
+  </si>
+  <si>
+    <t>samsung mobiles</t>
+  </si>
+  <si>
+    <t>apple mobiles</t>
   </si>
 </sst>
 </file>
@@ -351,8 +357,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -369,6 +378,16 @@
         <v>2</v>
       </c>
     </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Excelfile/ItemDetails.xlsx
+++ b/Excelfile/ItemDetails.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\InfoEge Automation Project\Feb_26-Practice_ArtifactID\Excelfile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F80B9FC9-596D-4106-82E2-41177CB9E9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78628248-0585-43A0-B800-5092AF2391DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,16 +30,16 @@
     <t>items</t>
   </si>
   <si>
-    <t>gift</t>
-  </si>
-  <si>
-    <t>shirts</t>
-  </si>
-  <si>
-    <t>samsung mobiles</t>
-  </si>
-  <si>
-    <t>apple mobiles</t>
+    <t>spyker</t>
+  </si>
+  <si>
+    <t>Wranglar</t>
+  </si>
+  <si>
+    <t>ether</t>
+  </si>
+  <si>
+    <t>pepe</t>
   </si>
 </sst>
 </file>
